--- a/data/00992A_20260826.xlsx
+++ b/data/00992A_20260826.xlsx
@@ -384,7 +384,7 @@
         <v>基金淨資產價值(元)</v>
       </c>
       <c r="B1" t="str">
-        <v>TWD 42,364,815,694</v>
+        <v>TWD 43,588,592,385</v>
       </c>
     </row>
     <row r="2">
@@ -392,7 +392,7 @@
         <v>每受益權單位淨資產價值(元)-台幣交易</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD 17.7</v>
+        <v>TWD 18.21</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +436,7 @@
         <v>川湖</v>
       </c>
       <c r="C2" t="str">
-        <v>8.77%</v>
+        <v>8.66%</v>
       </c>
       <c r="D2" t="str">
         <v>260,000</v>
@@ -444,30 +444,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2330</v>
+        <v>3017</v>
       </c>
       <c r="B3" t="str">
-        <v>台積電</v>
+        <v>奇鋐</v>
       </c>
       <c r="C3" t="str">
-        <v>7.4%</v>
+        <v>7.25%</v>
       </c>
       <c r="D3" t="str">
-        <v>1,306,000</v>
+        <v>1,001,000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3017</v>
+        <v>2330</v>
       </c>
       <c r="B4" t="str">
-        <v>奇鋐</v>
+        <v>台積電</v>
       </c>
       <c r="C4" t="str">
-        <v>6.97%</v>
+        <v>7.24%</v>
       </c>
       <c r="D4" t="str">
-        <v>1,001,000</v>
+        <v>1,306,000</v>
       </c>
     </row>
     <row r="5">
@@ -478,7 +478,7 @@
         <v>欣興</v>
       </c>
       <c r="C5" t="str">
-        <v>6.42%</v>
+        <v>6.61%</v>
       </c>
       <c r="D5" t="str">
         <v>2,482,000</v>
@@ -492,7 +492,7 @@
         <v>台光電</v>
       </c>
       <c r="C6" t="str">
-        <v>6.14%</v>
+        <v>6.29%</v>
       </c>
       <c r="D6" t="str">
         <v>465,000</v>
@@ -506,7 +506,7 @@
         <v>貿聯-KY</v>
       </c>
       <c r="C7" t="str">
-        <v>5.69%</v>
+        <v>5.34%</v>
       </c>
       <c r="D7" t="str">
         <v>1,161,000</v>
@@ -520,7 +520,7 @@
         <v>智邦</v>
       </c>
       <c r="C8" t="str">
-        <v>5.15%</v>
+        <v>5.06%</v>
       </c>
       <c r="D8" t="str">
         <v>1,074,000</v>
@@ -528,30 +528,30 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8996</v>
+        <v>3008</v>
       </c>
       <c r="B9" t="str">
-        <v>高力</v>
+        <v>大立光</v>
       </c>
       <c r="C9" t="str">
-        <v>4.67%</v>
+        <v>4.95%</v>
       </c>
       <c r="D9" t="str">
-        <v>1,630,000</v>
+        <v>343,000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>3008</v>
+        <v>8996</v>
       </c>
       <c r="B10" t="str">
-        <v>大立光</v>
+        <v>高力</v>
       </c>
       <c r="C10" t="str">
-        <v>4.63%</v>
+        <v>4.47%</v>
       </c>
       <c r="D10" t="str">
-        <v>343,000</v>
+        <v>1,630,000</v>
       </c>
     </row>
     <row r="11">
@@ -562,7 +562,7 @@
         <v>旺矽</v>
       </c>
       <c r="C11" t="str">
-        <v>3.54%</v>
+        <v>3.1%</v>
       </c>
       <c r="D11" t="str">
         <v>268,000</v>
@@ -576,7 +576,7 @@
         <v>南俊國際</v>
       </c>
       <c r="C12" t="str">
-        <v>3.13%</v>
+        <v>3.09%</v>
       </c>
       <c r="D12" t="str">
         <v>2,231,000</v>
@@ -590,7 +590,7 @@
         <v>緯創</v>
       </c>
       <c r="C13" t="str">
-        <v>3.05%</v>
+        <v>3.03%</v>
       </c>
       <c r="D13" t="str">
         <v>7,245,000</v>
@@ -604,7 +604,7 @@
         <v>富喬</v>
       </c>
       <c r="C14" t="str">
-        <v>2.8%</v>
+        <v>2.94%</v>
       </c>
       <c r="D14" t="str">
         <v>10,877,000</v>
@@ -618,7 +618,7 @@
         <v>全新</v>
       </c>
       <c r="C15" t="str">
-        <v>2.73%</v>
+        <v>2.7%</v>
       </c>
       <c r="D15" t="str">
         <v>2,753,000</v>
@@ -626,44 +626,44 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8021</v>
+        <v>1303</v>
       </c>
       <c r="B16" t="str">
-        <v>尖點</v>
+        <v>南亞</v>
       </c>
       <c r="C16" t="str">
-        <v>2.56%</v>
+        <v>2.59%</v>
       </c>
       <c r="D16" t="str">
-        <v>2,682,000</v>
+        <v>5,445,000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2308</v>
+        <v>8021</v>
       </c>
       <c r="B17" t="str">
-        <v>台達電</v>
+        <v>尖點</v>
       </c>
       <c r="C17" t="str">
-        <v>2.55%</v>
+        <v>2.58%</v>
       </c>
       <c r="D17" t="str">
-        <v>632,000</v>
+        <v>2,682,000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1303</v>
+        <v>2308</v>
       </c>
       <c r="B18" t="str">
-        <v>南亞</v>
+        <v>台達電</v>
       </c>
       <c r="C18" t="str">
-        <v>2.42%</v>
+        <v>2.54%</v>
       </c>
       <c r="D18" t="str">
-        <v>5,445,000</v>
+        <v>632,000</v>
       </c>
     </row>
     <row r="19">
@@ -674,7 +674,7 @@
         <v>聯發科</v>
       </c>
       <c r="C19" t="str">
-        <v>2.35%</v>
+        <v>2.41%</v>
       </c>
       <c r="D19" t="str">
         <v>266,000</v>
@@ -688,7 +688,7 @@
         <v>創意</v>
       </c>
       <c r="C20" t="str">
-        <v>2.16%</v>
+        <v>2.3%</v>
       </c>
       <c r="D20" t="str">
         <v>164,000</v>
@@ -702,7 +702,7 @@
         <v>世芯-KY</v>
       </c>
       <c r="C21" t="str">
-        <v>1.96%</v>
+        <v>1.95%</v>
       </c>
       <c r="D21" t="str">
         <v>215,000</v>
@@ -716,7 +716,7 @@
         <v>景碩</v>
       </c>
       <c r="C22" t="str">
-        <v>1.66%</v>
+        <v>1.71%</v>
       </c>
       <c r="D22" t="str">
         <v>844,013</v>
@@ -730,7 +730,7 @@
         <v>緯穎</v>
       </c>
       <c r="C23" t="str">
-        <v>1.17%</v>
+        <v>1.2%</v>
       </c>
       <c r="D23" t="str">
         <v>77,000</v>
@@ -744,7 +744,7 @@
         <v>臻鼎-KY</v>
       </c>
       <c r="C24" t="str">
-        <v>1.05%</v>
+        <v>1.04%</v>
       </c>
       <c r="D24" t="str">
         <v>1,000,000</v>
@@ -758,7 +758,7 @@
         <v>日月光投控</v>
       </c>
       <c r="C25" t="str">
-        <v>1%</v>
+        <v>0.97%</v>
       </c>
       <c r="D25" t="str">
         <v>716,000</v>
@@ -772,7 +772,7 @@
         <v>南電</v>
       </c>
       <c r="C26" t="str">
-        <v>0.82%</v>
+        <v>0.81%</v>
       </c>
       <c r="D26" t="str">
         <v>300,000</v>
@@ -786,7 +786,7 @@
         <v>聯茂</v>
       </c>
       <c r="C27" t="str">
-        <v>0.47%</v>
+        <v>0.5%</v>
       </c>
       <c r="D27" t="str">
         <v>373,000</v>
@@ -794,44 +794,44 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2301</v>
+        <v>3081</v>
       </c>
       <c r="B28" t="str">
-        <v>光寶科</v>
+        <v>聯亞</v>
       </c>
       <c r="C28" t="str">
-        <v>0.46%</v>
+        <v>0.47%</v>
       </c>
       <c r="D28" t="str">
-        <v>659,000</v>
+        <v>63,000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6139</v>
+        <v>2301</v>
       </c>
       <c r="B29" t="str">
-        <v>亞翔</v>
+        <v>光寶科</v>
       </c>
       <c r="C29" t="str">
-        <v>0.45%</v>
+        <v>0.46%</v>
       </c>
       <c r="D29" t="str">
-        <v>250,000</v>
+        <v>659,000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>3081</v>
+        <v>6139</v>
       </c>
       <c r="B30" t="str">
-        <v>聯亞</v>
+        <v>亞翔</v>
       </c>
       <c r="C30" t="str">
-        <v>0.44%</v>
+        <v>0.46%</v>
       </c>
       <c r="D30" t="str">
-        <v>63,000</v>
+        <v>250,000</v>
       </c>
     </row>
     <row r="31">
@@ -842,7 +842,7 @@
         <v>華碩</v>
       </c>
       <c r="C31" t="str">
-        <v>0.43%</v>
+        <v>0.44%</v>
       </c>
       <c r="D31" t="str">
         <v>196,000</v>
@@ -850,30 +850,30 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2376</v>
+        <v>3653</v>
       </c>
       <c r="B32" t="str">
-        <v>技嘉</v>
+        <v>健策</v>
       </c>
       <c r="C32" t="str">
-        <v>0.42%</v>
+        <v>0.43%</v>
       </c>
       <c r="D32" t="str">
-        <v>508,000</v>
+        <v>33,000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>3653</v>
+        <v>2376</v>
       </c>
       <c r="B33" t="str">
-        <v>健策</v>
+        <v>技嘉</v>
       </c>
       <c r="C33" t="str">
         <v>0.41%</v>
       </c>
       <c r="D33" t="str">
-        <v>33,000</v>
+        <v>508,000</v>
       </c>
     </row>
     <row r="34">
@@ -884,7 +884,7 @@
         <v>南茂</v>
       </c>
       <c r="C34" t="str">
-        <v>0.4%</v>
+        <v>0.41%</v>
       </c>
       <c r="D34" t="str">
         <v>1,957,000</v>
@@ -906,30 +906,30 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>5274</v>
+        <v>6274</v>
       </c>
       <c r="B36" t="str">
-        <v>信驊</v>
+        <v>台燿</v>
       </c>
       <c r="C36" t="str">
         <v>0.4%</v>
       </c>
       <c r="D36" t="str">
-        <v>11,000</v>
+        <v>113,000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6274</v>
+        <v>5274</v>
       </c>
       <c r="B37" t="str">
-        <v>台燿</v>
+        <v>信驊</v>
       </c>
       <c r="C37" t="str">
         <v>0.4%</v>
       </c>
       <c r="D37" t="str">
-        <v>113,000</v>
+        <v>11,000</v>
       </c>
     </row>
     <row r="38">
@@ -940,7 +940,7 @@
         <v>漢唐</v>
       </c>
       <c r="C38" t="str">
-        <v>0.39%</v>
+        <v>0.38%</v>
       </c>
       <c r="D38" t="str">
         <v>155,000</v>
@@ -954,7 +954,7 @@
         <v>禾伸堂</v>
       </c>
       <c r="C39" t="str">
-        <v>0.39%</v>
+        <v>0.37%</v>
       </c>
       <c r="D39" t="str">
         <v>261,000</v>
@@ -982,7 +982,7 @@
         <v>宜鼎</v>
       </c>
       <c r="C41" t="str">
-        <v>0.35%</v>
+        <v>0.34%</v>
       </c>
       <c r="D41" t="str">
         <v>98,000</v>
